--- a/006_資源マネジメント/アサイン表.xlsx
+++ b/006_資源マネジメント/アサイン表.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/project-management-toolbox/006_資源マネジメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BF36BD-26FF-6449-B70C-7A0F706A2BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CED7C2-534A-544B-9481-AA473A043BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32780" yWindow="1420" windowWidth="28300" windowHeight="16940" xr2:uid="{2A5B3926-B251-2F46-8D94-562C30265314}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{2A5B3926-B251-2F46-8D94-562C30265314}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="5" r:id="rId1"/>
     <sheet name="データ" sheetId="1" r:id="rId2"/>
     <sheet name="人別" sheetId="7" r:id="rId3"/>
     <sheet name="プロジェクト別" sheetId="10" r:id="rId4"/>
+    <sheet name="マスタ" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">データ!$B$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="62" r:id="rId5"/>
+    <pivotCache cacheId="19" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>田中</t>
   </si>
@@ -89,13 +90,6 @@
   <si>
     <t>鈴木</t>
     <rPh sb="0" eb="2">
-      <t xml:space="preserve">スズキ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鈴木</t>
-    <rPh sb="0" eb="1">
       <t xml:space="preserve">スズキ </t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -206,21 +200,8 @@
   </si>
   <si>
     <t>林</t>
-  </si>
-  <si>
-    <t>林</t>
     <rPh sb="0" eb="1">
       <t xml:space="preserve">ハヤシ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>会計</t>
-  </si>
-  <si>
-    <t>会計</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">カイケイ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -358,6 +339,20 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>要員氏名</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヨウイン </t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">シメイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -441,7 +436,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -478,6 +473,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -487,7 +497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -503,12 +513,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -517,6 +521,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -535,7 +548,919 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="192">
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Meiryo UI"/>
@@ -1096,29 +2021,24 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tanaka Hideaki" refreshedDate="45325.420873495372" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{43A74667-4A75-724F-8E0E-59AD986E1342}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tanaka Hideaki" refreshedDate="45745.544456828706" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{43A74667-4A75-724F-8E0E-59AD986E1342}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:F1000" sheet="データ"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="稼働年月" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-01-01T00:00:00" maxDate="2024-03-02T00:00:00" count="4">
-        <d v="2024-01-01T00:00:00"/>
-        <d v="2024-02-01T00:00:00"/>
-        <d v="2024-03-01T00:00:00"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-01-01T00:00:00" maxDate="2024-03-02T00:00:00"/>
     </cacheField>
     <cacheField name="氏名" numFmtId="0">
       <sharedItems containsBlank="1" count="8">
-        <s v="田中"/>
-        <s v="佐藤"/>
+        <s v="伊藤"/>
         <s v="山田"/>
         <s v="鈴木"/>
         <s v="高橋"/>
-        <s v="伊藤"/>
-        <s v="林"/>
+        <s v="田中"/>
+        <s v="佐藤"/>
         <m/>
+        <s v="林" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="仕事" numFmtId="0">
@@ -1126,8 +2046,8 @@
         <s v="プロジェクトA"/>
         <s v="プロジェクトB"/>
         <s v="プロジェクトC"/>
-        <s v="会計"/>
         <m/>
+        <s v="会計" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="稼働工数" numFmtId="0">
@@ -1154,9 +2074,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="20">
   <r>
-    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
     <n v="0.2"/>
@@ -1164,7 +2084,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
     <x v="0"/>
     <x v="1"/>
     <n v="0.4"/>
@@ -1172,15 +2092,15 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
     <x v="1"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="0.8"/>
     <n v="2024"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
     <n v="0.1"/>
@@ -1188,15 +2108,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="0.1"/>
-    <n v="2024"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="1"/>
+    <d v="2024-02-01T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
     <n v="0.1"/>
@@ -1204,49 +2116,121 @@
     <x v="1"/>
   </r>
   <r>
+    <d v="2024-02-01T00:00:00"/>
+    <x v="2"/>
     <x v="1"/>
+    <n v="0.1"/>
+    <n v="2024"/>
     <x v="1"/>
+  </r>
+  <r>
+    <d v="2024-02-01T00:00:00"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="0.8"/>
     <n v="2024"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="2"/>
+    <d v="2024-03-01T00:00:00"/>
     <x v="1"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="0.8"/>
     <n v="2024"/>
     <x v="2"/>
   </r>
   <r>
+    <d v="2024-01-01T00:00:00"/>
+    <x v="5"/>
     <x v="0"/>
-    <x v="4"/>
-    <x v="2"/>
     <n v="1"/>
     <n v="2024"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
     <n v="0.9"/>
     <n v="2024"/>
     <x v="0"/>
   </r>
   <r>
+    <d v="2024-01-01T00:00:00"/>
+    <x v="2"/>
     <x v="0"/>
-    <x v="6"/>
-    <x v="3"/>
     <n v="1"/>
     <n v="2024"/>
     <x v="0"/>
   </r>
   <r>
+    <m/>
+    <x v="6"/>
     <x v="3"/>
-    <x v="7"/>
-    <x v="4"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+  </r>
+  <r>
+    <m/>
+    <x v="6"/>
+    <x v="3"/>
     <m/>
     <m/>
     <x v="3"/>
@@ -1255,20 +2239,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFC175F5-D21E-224A-B46F-12A64F70359E}" name="ピボットテーブル2" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFC175F5-D21E-224A-B46F-12A64F70359E}" name="ピボットテーブル2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="9">
+        <item x="0"/>
+        <item x="3"/>
         <item x="5"/>
+        <item x="1"/>
         <item x="4"/>
-        <item x="1"/>
+        <item m="1" x="7"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item h="1" x="7"/>
+        <item h="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1277,8 +2261,8 @@
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item m="1" x="4"/>
         <item x="3"/>
-        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1298,33 +2282,9 @@
     <field x="1"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="17">
+  <rowItems count="15">
     <i>
       <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i r="1">
       <x/>
@@ -1333,10 +2293,28 @@
       <x v="1"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
       <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
     </i>
     <i>
       <x v="6"/>
@@ -1372,7 +2350,7 @@
     <dataField name="合計 / 稼働工数" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="34">
-    <format dxfId="47">
+    <format dxfId="191">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1382,7 +2360,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="190">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1395,7 +2373,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="189">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1405,7 +2383,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="188">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1418,7 +2396,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="187">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1428,7 +2406,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="186">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1441,7 +2419,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="185">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1451,7 +2429,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="184">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1464,7 +2442,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="183">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1474,7 +2452,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="182">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1488,7 +2466,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="181">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1498,7 +2476,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="180">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1511,7 +2489,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="179">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1521,7 +2499,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="178">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1535,7 +2513,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="177">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -1545,7 +2523,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="176">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="1" count="1" selected="0">
@@ -1558,35 +2536,35 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="175">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="174">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="173">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="172">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="171">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="170">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="169">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="168">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="167">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1598,7 +2576,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="166">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1610,7 +2588,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="165">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1622,7 +2600,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="164">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1634,7 +2612,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="163">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1647,7 +2625,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="162">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1659,7 +2637,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="161">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1672,7 +2650,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="160">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -1684,14 +2662,14 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="159">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="158">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1996,28 +2974,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D383E727-DE33-054E-9487-80CADC2F8EE8}" name="ピボットテーブル3" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D383E727-DE33-054E-9487-80CADC2F8EE8}" name="ピボットテーブル3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="9">
+        <item x="0"/>
+        <item x="3"/>
         <item x="5"/>
+        <item x="1"/>
         <item x="4"/>
-        <item x="1"/>
+        <item m="1" x="7"/>
         <item x="2"/>
-        <item x="0"/>
         <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2026,8 +2996,8 @@
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item x="3"/>
-        <item h="1" x="4"/>
+        <item m="1" x="4"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2047,7 +3017,7 @@
     <field x="2"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="14">
+  <rowItems count="12">
     <i>
       <x/>
     </i>
@@ -2055,10 +3025,7 @@
       <x/>
     </i>
     <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
+      <x v="2"/>
     </i>
     <i r="1">
       <x v="6"/>
@@ -2067,7 +3034,13 @@
       <x v="1"/>
     </i>
     <i r="1">
-      <x v="4"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
     </i>
     <i r="1">
       <x v="6"/>
@@ -2076,16 +3049,7 @@
       <x v="2"/>
     </i>
     <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -2112,35 +3076,35 @@
     <dataField name="合計 / 稼働工数" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="13">
+    <format dxfId="157">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="156">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="155">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="154">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="153">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="152">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="151">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="150">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="149">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="4">
@@ -2155,7 +3119,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="148">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -2168,7 +3132,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="147">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -2181,7 +3145,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="146">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1">
@@ -2193,7 +3157,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="145">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="3">
@@ -2204,7 +3168,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="144">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2671,47 +3635,47 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="B49" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="19">
@@ -2719,22 +3683,22 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="C66" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="C67" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +3720,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -2767,7 +3731,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
@@ -2776,256 +3740,320 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5">
+      <c r="A2" s="8">
         <v>45292</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="B2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="9">
         <v>0.2</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="10">
         <f>YEAR(A2)</f>
         <v>2024</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="10">
         <f t="shared" ref="F2:F12" si="0">MONTH(A2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="5">
+      <c r="A3" s="8">
         <v>45292</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="B3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="9">
         <v>0.4</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="10">
         <f t="shared" ref="E3:E9" si="1">YEAR(A3)</f>
         <v>2024</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5">
+      <c r="A4" s="8">
         <v>45292</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="9">
         <v>0.8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5">
+      <c r="A5" s="8">
         <v>45292</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="B5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="9">
         <v>0.1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5">
+      <c r="A6" s="8">
         <v>45323</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="9">
         <v>0.1</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5">
+      <c r="A7" s="8">
         <v>45323</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5">
+      <c r="A8" s="8">
         <v>45323</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="D8" s="9">
         <v>0.8</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5">
+      <c r="A9" s="8">
         <v>45352</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="9">
         <v>0.8</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="10">
         <f t="shared" si="1"/>
         <v>2024</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5">
+      <c r="A10" s="8">
         <v>45292</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
         <v>1</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="10">
         <f t="shared" ref="E10" si="2">YEAR(A10)</f>
         <v>2024</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5">
+      <c r="A11" s="8">
         <v>45292</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9">
         <v>0.9</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="10">
         <f t="shared" ref="E11" si="3">YEAR(A11)</f>
         <v>2024</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5">
+      <c r="A12" s="8">
         <v>45292</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="10">
         <f t="shared" ref="E12" si="4">YEAR(A12)</f>
         <v>2024</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:D12" xr:uid="{911ABC2A-0236-6A44-9070-5C2ACC8DFF00}"/>
@@ -3035,6 +4063,24 @@
   <headerFooter>
     <oddFooter>&amp;R&amp;"游ゴシック Regular,標準"&amp;K000000© 2024 Hideaki Tanaka</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F16E9BAC-7061-C945-B86B-7386C2271D98}">
+          <x14:formula1>
+            <xm:f>マスタ!$A$2:$A$100</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E2273F26-6AD2-B344-9371-D7071A8F030C}">
+          <x14:formula1>
+            <xm:f>マスタ!$B$2:$B$100</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C20</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -3047,23 +4093,23 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="6" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6" ht="20">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" ht="20">
-      <c r="A4" s="7" t="s">
-        <v>23</v>
+      <c r="A4" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -3075,261 +4121,249 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" ht="20">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="A5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" ht="20">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:6" ht="20">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" ht="20">
+      <c r="A8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" ht="20">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:6" ht="20">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:6" ht="20">
+      <c r="A11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12" spans="1:6" ht="20">
+      <c r="A12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1.6</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" ht="20">
+      <c r="A13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1.6</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" ht="20">
+      <c r="A14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:6" ht="20">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" ht="20">
+      <c r="A16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11">
+        <v>2</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" ht="20">
+      <c r="A17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" ht="20">
+      <c r="A18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="11">
         <v>0.9</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" ht="20">
-      <c r="A6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" ht="20">
-      <c r="A7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="C18" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14">
         <v>1</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13">
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" ht="20">
+      <c r="A19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C19" s="14">
         <v>1</v>
       </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" ht="20">
-      <c r="A8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="10">
-        <v>1</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13">
-        <v>1</v>
-      </c>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" ht="20">
-      <c r="A9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10">
+      <c r="D19" s="14">
         <v>0.8</v>
       </c>
-      <c r="C9" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="D9" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="E9" s="13">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" ht="20">
-      <c r="A10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="E10" s="13">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" ht="20">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" ht="20">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" ht="20">
-      <c r="A13" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="10">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" ht="20">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="1:6" ht="20">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="1:6" ht="20">
-      <c r="A16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="10">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13">
-        <v>1</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" ht="20">
-      <c r="A17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="10">
-        <v>1</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13">
-        <v>1</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" ht="20">
-      <c r="A18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" ht="20">
-      <c r="A19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13">
-        <v>0.1</v>
+      <c r="E19" s="14">
+        <v>6.2000000000000011</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" ht="20">
-      <c r="A20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13">
-        <v>0.1</v>
-      </c>
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" ht="20">
-      <c r="A21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="13">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="E21" s="13">
-        <v>6.2</v>
-      </c>
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="20">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -3337,7 +4371,7 @@
       <c r="E22"/>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="20">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -3347,7 +4381,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting pivot="1" sqref="B5:D5 B6:D6 B7:D7 B8:D8 B9:D9 B10:D10 B11:D11 B12:D12 B13:D13 B14:D15 B16:D16 B17:D17 B18:D18 B19:D20">
+  <conditionalFormatting pivot="1" sqref="B5:D5 B6:D6 B8:D8 B10:D10 B12:D12 B14:D14 B16:D16 B17:D18">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3380,7 +4414,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B5:D5 B6:D6 B7:D7 B8:D8 B9:D9 B10:D10 B11:D11 B12:D12 B13:D13 B14:D15 B16:D16 B17:D17 B18:D18 B19:D20</xm:sqref>
+          <xm:sqref>B5:D5 B6:D6 B8:D8 B10:D10 B12:D12 B14:D14 B16:D16 B17:D18</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3396,23 +4430,23 @@
   <dimension ref="A3:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.5703125" style="1" customWidth="1"/>
     <col min="5" max="6" width="5.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>23</v>
+      <c r="A4" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -3424,190 +4458,194 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="14">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="14">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14">
         <v>0.1</v>
       </c>
-      <c r="E5" s="1">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="14">
         <v>0.9</v>
       </c>
-      <c r="E6" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="C13" s="14">
         <v>0.1</v>
       </c>
-      <c r="E7" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="9" t="s">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14">
         <v>0.8</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14">
         <v>0.8</v>
       </c>
-      <c r="E13" s="1">
-        <v>3.4000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="1">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="D16" s="14">
         <v>0.8</v>
       </c>
-      <c r="C15" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2.4000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
+      <c r="E16" s="14">
+        <v>6.2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="E18" s="1">
-        <v>6.2000000000000011</v>
-      </c>
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting pivot="1" sqref="B5:D5 B6:D9 B10:D10 B11:D12 B13:D13 B14:D15 B16:D16 B17:D17">
+  <conditionalFormatting pivot="1" sqref="B5:D5 B6:D6 B8:D8 B9:D9 B13:D13 B14:D14">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3640,10 +4678,78 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B5:D5 B6:D9 B10:D10 B11:D12 B13:D13 B14:D15 B16:D16 B17:D17</xm:sqref>
+          <xm:sqref>B5:D5 B6:D6 B8:D8 B9:D9 B13:D13 B14:D14</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336905D1-B9EA-7744-AA4C-7739F8AC1370}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" style="1"/>
+    <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>